--- a/data/trans_dic/P56$familiar-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiar-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,18</t>
+          <t>0,0; 35,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,16; 60,04</t>
+          <t>9,14; 59,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,31; 42,37</t>
+          <t>4,79; 41,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,56; 78,0</t>
+          <t>50,06; 79,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,17</t>
+          <t>0,0; 41,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,12; 46,18</t>
+          <t>17,7; 46,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,21; 53,17</t>
+          <t>21,22; 55,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48,03; 63,36</t>
+          <t>46,61; 64,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 29,98</t>
+          <t>3,81; 31,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,26; 44,6</t>
+          <t>21,29; 45,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,83; 45,28</t>
+          <t>19,55; 44,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,38; 65,95</t>
+          <t>51,46; 65,11</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 47,76</t>
+          <t>6,7; 47,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,02; 44,19</t>
+          <t>10,75; 46,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,19; 54,84</t>
+          <t>13,35; 55,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,81; 78,09</t>
+          <t>49,18; 77,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,4; 52,8</t>
+          <t>13,18; 49,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,91; 47,51</t>
+          <t>22,5; 47,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 26,93</t>
+          <t>3,25; 27,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,26; 69,92</t>
+          <t>53,57; 69,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,93; 43,22</t>
+          <t>13,32; 43,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,72; 42,89</t>
+          <t>23,01; 41,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,33; 31,69</t>
+          <t>8,85; 30,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,66; 69,92</t>
+          <t>56,06; 69,56</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,24</t>
+          <t>0,0; 61,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 52,41</t>
+          <t>6,02; 54,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,44</t>
+          <t>0,0; 21,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,03; 60,31</t>
+          <t>22,17; 59,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,59; 49,55</t>
+          <t>5,88; 45,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,04; 34,19</t>
+          <t>9,98; 35,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,59; 38,69</t>
+          <t>10,06; 40,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,8; 66,96</t>
+          <t>43,96; 66,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,22; 43,35</t>
+          <t>8,64; 41,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,33; 33,69</t>
+          <t>11,72; 34,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 28,94</t>
+          <t>7,0; 28,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,57; 60,34</t>
+          <t>40,67; 60,55</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 50,21</t>
+          <t>6,29; 50,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 49,37</t>
+          <t>8,64; 47,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,86</t>
+          <t>0,0; 33,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,61; 48,31</t>
+          <t>23,36; 49,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,26</t>
+          <t>0,0; 24,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,18; 43,98</t>
+          <t>18,85; 43,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,31; 44,49</t>
+          <t>17,01; 46,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,07; 59,6</t>
+          <t>42,78; 58,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 25,88</t>
+          <t>5,33; 26,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,42; 39,79</t>
+          <t>18,31; 39,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,86; 38,18</t>
+          <t>14,64; 39,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40,23; 54,07</t>
+          <t>39,35; 53,63</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,14; 32,15</t>
+          <t>10,28; 33,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,3; 37,43</t>
+          <t>16,04; 38,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,78; 26,46</t>
+          <t>9,76; 25,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42,17; 57,74</t>
+          <t>42,71; 57,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,23; 27,09</t>
+          <t>10,87; 28,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,79; 37,03</t>
+          <t>22,83; 36,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,0; 33,24</t>
+          <t>18,22; 32,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>51,84; 60,66</t>
+          <t>51,73; 60,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,33; 26,2</t>
+          <t>12,54; 26,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,59; 34,69</t>
+          <t>23,71; 34,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,99; 29,64</t>
+          <t>17,63; 28,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,26; 57,99</t>
+          <t>50,47; 57,9</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5522</t>
+          <t>0; 4710</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>970; 6357</t>
+          <t>968; 6342</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1007; 8040</t>
+          <t>909; 7902</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12438; 19574</t>
+          <t>12563; 19844</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6747</t>
+          <t>0; 6844</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8353; 21294</t>
+          <t>8160; 21439</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8446; 21172</t>
+          <t>8450; 21911</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29705; 39188</t>
+          <t>28826; 39845</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1134; 8838</t>
+          <t>1122; 9259</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11487; 25286</t>
+          <t>12069; 25603</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11661; 26622</t>
+          <t>11492; 26076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44673; 57341</t>
+          <t>44737; 56603</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1007; 7148</t>
+          <t>1003; 7093</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4217; 14316</t>
+          <t>3482; 15067</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2768; 10692</t>
+          <t>2602; 10845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11924; 19074</t>
+          <t>12013; 18933</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3668; 14452</t>
+          <t>3607; 13619</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15702; 31200</t>
+          <t>14775; 31265</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1280; 11057</t>
+          <t>1336; 11286</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35638; 46784</t>
+          <t>35842; 46661</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5900; 18298</t>
+          <t>5639; 18415</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22282; 42060</t>
+          <t>22568; 40570</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6258; 19191</t>
+          <t>5360; 18274</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49925; 63867</t>
+          <t>51202; 63539</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4329</t>
+          <t>0; 4309</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>904; 7324</t>
+          <t>842; 7593</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3944</t>
+          <t>0; 3825</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4471; 12240</t>
+          <t>4499; 12032</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1163; 8744</t>
+          <t>1037; 8111</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4238; 14426</t>
+          <t>4211; 15060</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2659; 13561</t>
+          <t>3526; 14349</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18916; 28272</t>
+          <t>18560; 28050</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2513; 10664</t>
+          <t>2124; 10245</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6366; 18927</t>
+          <t>6586; 19586</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3619; 15230</t>
+          <t>3684; 14903</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25367; 37725</t>
+          <t>25429; 37854</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>833; 6662</t>
+          <t>835; 6647</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1868; 10636</t>
+          <t>1861; 10164</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5272</t>
+          <t>0; 5370</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7290; 15575</t>
+          <t>7532; 15815</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7476</t>
+          <t>0; 7774</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9319; 22551</t>
+          <t>9664; 22441</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9108; 24849</t>
+          <t>9501; 26053</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34476; 47711</t>
+          <t>34243; 47178</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2436; 11753</t>
+          <t>2420; 12168</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13415; 28973</t>
+          <t>13333; 28963</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10688; 27455</t>
+          <t>10527; 28358</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45179; 60719</t>
+          <t>44188; 60228</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5379; 15524</t>
+          <t>4961; 16299</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12799; 29383</t>
+          <t>12593; 29885</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7052; 19077</t>
+          <t>7036; 18674</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43036; 58931</t>
+          <t>43587; 58844</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10506; 25341</t>
+          <t>10165; 26329</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>48827; 76005</t>
+          <t>46863; 74566</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32633; 57110</t>
+          <t>31293; 56105</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>130128; 152263</t>
+          <t>129858; 152218</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18898; 37160</t>
+          <t>17788; 37377</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66930; 98422</t>
+          <t>67265; 97332</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43864; 72276</t>
+          <t>42987; 70377</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>177458; 204769</t>
+          <t>178211; 204443</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$familiar-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiar-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>57,93%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,98</t>
+          <t>0,0; 42,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,14; 59,9</t>
+          <t>0,0; 59,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 41,65</t>
+          <t>4,34; 38,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,06; 79,07</t>
+          <t>48,2; 78,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,76</t>
+          <t>0,0; 35,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,7; 46,49</t>
+          <t>19,46; 46,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,22; 55,03</t>
+          <t>20,81; 52,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46,61; 64,43</t>
+          <t>46,13; 62,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 31,41</t>
+          <t>3,71; 30,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,29; 45,15</t>
+          <t>20,26; 45,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,55; 44,35</t>
+          <t>19,24; 44,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,46; 65,11</t>
+          <t>50,71; 65,29</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 47,39</t>
+          <t>6,75; 47,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,75; 46,51</t>
+          <t>12,88; 44,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,35; 55,62</t>
+          <t>14,0; 53,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,18; 77,51</t>
+          <t>47,97; 77,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,18; 49,76</t>
+          <t>12,91; 50,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,5; 47,61</t>
+          <t>22,38; 45,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 27,48</t>
+          <t>3,1; 27,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,57; 69,73</t>
+          <t>52,27; 68,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,32; 43,5</t>
+          <t>13,4; 41,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,01; 41,37</t>
+          <t>22,62; 41,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,85; 30,17</t>
+          <t>9,41; 30,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,06; 69,56</t>
+          <t>53,92; 68,98</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,95</t>
+          <t>0,0; 61,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 54,33</t>
+          <t>6,46; 55,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,76</t>
+          <t>0,0; 21,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,17; 59,28</t>
+          <t>22,67; 58,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,88; 45,97</t>
+          <t>6,0; 47,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,98; 35,69</t>
+          <t>9,94; 36,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,06; 40,94</t>
+          <t>7,34; 40,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43,96; 66,43</t>
+          <t>42,95; 65,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,64; 41,64</t>
+          <t>10,45; 41,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,72; 34,87</t>
+          <t>12,26; 35,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 28,32</t>
+          <t>6,83; 30,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,67; 60,55</t>
+          <t>39,79; 61,38</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,62%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 50,1</t>
+          <t>6,2; 50,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,64; 47,18</t>
+          <t>8,71; 46,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,47</t>
+          <t>0,0; 35,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,36; 49,05</t>
+          <t>21,27; 47,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,19</t>
+          <t>0,0; 25,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,85; 43,77</t>
+          <t>18,32; 44,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,01; 46,64</t>
+          <t>16,81; 45,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,78; 58,93</t>
+          <t>43,64; 59,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 26,8</t>
+          <t>5,66; 27,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,31; 39,77</t>
+          <t>17,59; 40,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,64; 39,44</t>
+          <t>16,02; 41,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,35; 53,63</t>
+          <t>39,4; 53,81</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,28; 33,76</t>
+          <t>11,73; 33,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,04; 38,07</t>
+          <t>17,48; 38,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,76; 25,9</t>
+          <t>9,72; 26,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42,71; 57,66</t>
+          <t>42,14; 57,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,87; 28,15</t>
+          <t>10,32; 27,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,83; 36,33</t>
+          <t>23,77; 36,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,22; 32,66</t>
+          <t>17,83; 32,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>51,73; 60,64</t>
+          <t>50,72; 60,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,54; 26,35</t>
+          <t>12,78; 26,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,71; 34,3</t>
+          <t>22,94; 34,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,63; 28,86</t>
+          <t>17,31; 29,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,47; 57,9</t>
+          <t>49,81; 58,07</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>16765</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34509</t>
+          <t>36465</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50919</t>
+          <t>53231</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4710</t>
+          <t>0; 5580</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>968; 6342</t>
+          <t>0; 6317</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>909; 7902</t>
+          <t>824; 7212</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12563; 19844</t>
+          <t>12573; 20357</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6844</t>
+          <t>0; 5877</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8160; 21439</t>
+          <t>8973; 21594</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8450; 21911</t>
+          <t>8287; 20814</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28826; 39845</t>
+          <t>30353; 41372</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1122; 9259</t>
+          <t>1095; 9026</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12069; 25603</t>
+          <t>11485; 25776</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11492; 26076</t>
+          <t>11311; 26000</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44737; 56603</t>
+          <t>46594; 59998</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41548</t>
+          <t>45163</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57079</t>
+          <t>61841</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1003; 7093</t>
+          <t>1010; 7148</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3482; 15067</t>
+          <t>4173; 14471</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2602; 10845</t>
+          <t>2729; 10465</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12013; 18933</t>
+          <t>12594; 20298</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3607; 13619</t>
+          <t>3534; 13786</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14775; 31265</t>
+          <t>14693; 30191</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1336; 11286</t>
+          <t>1273; 11422</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35842; 46661</t>
+          <t>38699; 50804</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5639; 18415</t>
+          <t>5675; 17518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22568; 40570</t>
+          <t>22185; 41127</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5360; 18274</t>
+          <t>5697; 18763</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51202; 63539</t>
+          <t>54076; 69182</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>9018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23763</t>
+          <t>25948</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31722</t>
+          <t>34966</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4309</t>
+          <t>0; 4288</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>842; 7593</t>
+          <t>903; 7703</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3825</t>
+          <t>0; 3821</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4499; 12032</t>
+          <t>5241; 13620</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1037; 8111</t>
+          <t>1058; 8390</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4211; 15060</t>
+          <t>4194; 15377</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3526; 14349</t>
+          <t>2574; 14149</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18560; 28050</t>
+          <t>20481; 31316</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2124; 10245</t>
+          <t>2572; 10327</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6586; 19586</t>
+          <t>6889; 19845</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3684; 14903</t>
+          <t>3593; 15840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25429; 37854</t>
+          <t>28173; 43463</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11253</t>
+          <t>11326</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>45095</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>52267</t>
+          <t>56420</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>835; 6647</t>
+          <t>823; 6634</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1861; 10164</t>
+          <t>1876; 10104</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5370</t>
+          <t>0; 5723</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7532; 15815</t>
+          <t>7043; 15860</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7774</t>
+          <t>0; 8225</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9664; 22441</t>
+          <t>9392; 22684</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9501; 26053</t>
+          <t>9390; 25302</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34243; 47178</t>
+          <t>38360; 52685</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2420; 12168</t>
+          <t>2568; 12477</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13333; 28963</t>
+          <t>12811; 29673</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10527; 28358</t>
+          <t>11521; 29616</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44188; 60228</t>
+          <t>47681; 65121</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51152</t>
+          <t>53787</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>140834</t>
+          <t>152671</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>191987</t>
+          <t>206457</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4961; 16299</t>
+          <t>5663; 16148</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12593; 29885</t>
+          <t>13724; 29980</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7036; 18674</t>
+          <t>7008; 19030</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43587; 58844</t>
+          <t>45758; 62271</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10165; 26329</t>
+          <t>9655; 25607</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46863; 74566</t>
+          <t>48778; 74875</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31293; 56105</t>
+          <t>30624; 55836</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>129858; 152218</t>
+          <t>139710; 165284</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17788; 37377</t>
+          <t>18120; 37429</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67265; 97332</t>
+          <t>65087; 96671</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42987; 70377</t>
+          <t>42208; 71623</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>178211; 204443</t>
+          <t>191274; 222974</t>
         </is>
       </c>
     </row>
